--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Signature.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Signature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="233">
   <si>
     <t>Property</t>
   </si>
@@ -364,6 +364,9 @@
     <t>closed</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Signature.type:AuthorsSignature</t>
   </si>
   <si>
@@ -480,6 +483,9 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -574,6 +580,13 @@
   </si>
   <si>
     <t>A reference to an application-usable description of the identity that signed  (e.g. the signature used their private key).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Signature.who.id</t>
@@ -1080,7 +1093,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1603,24 +1616,24 @@
         <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>101</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>73</v>
@@ -1677,13 +1690,13 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
         <v>108</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
@@ -1710,21 +1723,21 @@
         <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1824,10 +1837,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1929,10 +1942,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1955,26 +1968,26 @@
         <v>102</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>73</v>
@@ -2016,7 +2029,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -2031,15 +2044,15 @@
         <v>81</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2065,13 +2078,13 @@
         <v>85</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2121,7 +2134,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2136,15 +2149,15 @@
         <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2167,24 +2180,24 @@
         <v>102</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>73</v>
@@ -2226,7 +2239,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2241,15 +2254,15 @@
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2275,14 +2288,16 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2331,7 +2346,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2346,15 +2361,15 @@
         <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2377,19 +2392,19 @@
         <v>102</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2438,7 +2453,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2453,18 +2468,18 @@
         <v>81</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>73</v>
@@ -2521,13 +2536,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y14" t="s" s="2">
         <v>108</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -2554,21 +2569,21 @@
         <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2668,10 +2683,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2773,10 +2788,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2799,26 +2814,26 @@
         <v>102</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>73</v>
@@ -2860,7 +2875,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2875,15 +2890,15 @@
         <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2909,13 +2924,13 @@
         <v>85</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2965,7 +2980,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2980,15 +2995,15 @@
         <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3011,24 +3026,24 @@
         <v>102</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>73</v>
@@ -3070,7 +3085,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3085,15 +3100,15 @@
         <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3119,14 +3134,16 @@
         <v>85</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -3175,7 +3192,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3190,15 +3207,15 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3221,19 +3238,19 @@
         <v>102</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3282,7 +3299,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3297,15 +3314,15 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3328,16 +3345,16 @@
         <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3387,7 +3404,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -3407,10 +3424,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3433,16 +3450,16 @@
         <v>102</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3492,7 +3509,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -3501,21 +3518,21 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>73</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3615,10 +3632,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3720,10 +3737,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3749,13 +3766,13 @@
         <v>85</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3805,7 +3822,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3814,7 +3831,7 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>81</v>
@@ -3825,10 +3842,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3851,16 +3868,16 @@
         <v>102</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3886,13 +3903,13 @@
         <v>73</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3910,7 +3927,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3930,10 +3947,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3956,16 +3973,16 @@
         <v>102</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4015,7 +4032,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4024,21 +4041,21 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4064,13 +4081,13 @@
         <v>85</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4120,7 +4137,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4140,10 +4157,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4166,19 +4183,19 @@
         <v>102</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -4227,7 +4244,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4236,21 +4253,21 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>73</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4273,16 +4290,16 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4311,28 +4328,28 @@
         <v>107</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4352,10 +4369,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4378,13 +4395,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4414,10 +4431,10 @@
         <v>107</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>73</v>
@@ -4435,7 +4452,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4455,10 +4472,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4481,16 +4498,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4540,7 +4557,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Signature.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Signature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="229">
   <si>
     <t>Property</t>
   </si>
@@ -364,9 +364,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Signature.type:AuthorsSignature</t>
   </si>
   <si>
@@ -483,9 +480,6 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -580,13 +574,6 @@
   </si>
   <si>
     <t>A reference to an application-usable description of the identity that signed  (e.g. the signature used their private key).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Signature.who.id</t>
@@ -1093,7 +1080,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1616,24 +1603,24 @@
         <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>101</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>73</v>
@@ -1690,13 +1677,13 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
         <v>108</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
@@ -1723,21 +1710,21 @@
         <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1837,10 +1824,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1942,10 +1929,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1968,68 +1955,68 @@
         <v>102</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="N9" t="s" s="2">
+      <c r="O9" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -2044,15 +2031,15 @@
         <v>81</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2078,13 +2065,13 @@
         <v>85</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2134,7 +2121,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2149,15 +2136,15 @@
         <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2180,66 +2167,66 @@
         <v>102</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2254,15 +2241,15 @@
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2288,16 +2275,14 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2346,7 +2331,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2361,15 +2346,15 @@
         <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2392,19 +2377,19 @@
         <v>102</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2453,7 +2438,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2468,18 +2453,18 @@
         <v>81</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>73</v>
@@ -2536,13 +2521,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y14" t="s" s="2">
         <v>108</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -2569,21 +2554,21 @@
         <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2683,10 +2668,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2788,10 +2773,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2814,68 +2799,68 @@
         <v>102</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2890,15 +2875,15 @@
         <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2924,13 +2909,13 @@
         <v>85</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2980,7 +2965,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2995,15 +2980,15 @@
         <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3026,24 +3011,24 @@
         <v>102</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>73</v>
@@ -3085,7 +3070,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3100,15 +3085,15 @@
         <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3134,16 +3119,14 @@
         <v>85</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -3192,7 +3175,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3207,15 +3190,15 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3238,19 +3221,19 @@
         <v>102</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3299,7 +3282,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3314,15 +3297,15 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3345,16 +3328,16 @@
         <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3404,7 +3387,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -3424,10 +3407,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3450,16 +3433,16 @@
         <v>102</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="N23" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3509,7 +3492,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -3518,21 +3501,21 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>184</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3632,10 +3615,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3737,10 +3720,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3766,13 +3749,13 @@
         <v>85</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3822,7 +3805,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3831,7 +3814,7 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>81</v>
@@ -3842,10 +3825,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3868,16 +3851,16 @@
         <v>102</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3903,13 +3886,13 @@
         <v>73</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3927,7 +3910,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3947,10 +3930,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3973,16 +3956,16 @@
         <v>102</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4032,7 +4015,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4041,21 +4024,21 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4081,13 +4064,13 @@
         <v>85</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4137,7 +4120,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4157,10 +4140,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4183,19 +4166,19 @@
         <v>102</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -4244,7 +4227,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4253,21 +4236,21 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>184</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4290,16 +4273,16 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4328,10 +4311,10 @@
         <v>107</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4349,7 +4332,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4369,10 +4352,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4395,13 +4378,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4431,10 +4414,10 @@
         <v>107</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>73</v>
@@ -4452,7 +4435,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4472,10 +4455,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4498,16 +4481,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4557,7 +4540,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
